--- a/TESTS/zlit_5_sindbad.xlsx
+++ b/TESTS/zlit_5_sindbad.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>З «Тисячі і однієї ночі» — великого збірника арабських казок</t>
+          <t>З «Тисячі і однієї ночі»</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>«Тисяча і одна ніч» — класичний збірник арабського фольклору де Шахразада розповідає казки</t>
+          <t>«Тисяча і одна ніч»</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Арабської — казка є частиною скарбниці арабського фольклору «Тисяча і одна ніч»</t>
+          <t>Арабської</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Сім — кожна наповнена небезпеками і дивовижними пригодами</t>
+          <t>Сім</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Спрага пригод і прагнення збагатіння — незважаючи на небезпеки його завжди вабило море</t>
+          <t>Спрага пригод і прагнення збагатіння</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Величезний кит що лежить нерухомо і якого мандрівники прийняли за острів — він раптово пірнув і всі впали у воду</t>
+          <t>Величезний кит що лежить нерухомо і якого мандрівники прийняли за острів</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Це був не острів а гігантський кит — від тепла вогню він прокинувся і пірнув</t>
+          <t>Це був не острів а гігантський кит</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Кому Сіндбад-Мореплавець розповідає про свої сім подорожей?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Халіфу</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бідному носильнику-тезці, що нарікав на свою важку долю біля його дому</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Своїй родині</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Морякам у порту</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому бідний носильник спершу позаздрив багатству Сіндбада?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо Сіндбад образив його</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо сам носильник тяжко працює за мізерну плату, а Сіндбад живе в розкоші</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо носильник теж був моряком</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо вони змагались за роботу</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що Сіндбад хотів довести носильнику, розповідаючи про свої подорожі?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що багатство дістається легко</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що його багатство — це плата за страшні небезпеки і випробування, яких пережив носильник і не уявляв</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що носильнику варто стати моряком</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого, просто розважав його</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що сталося з кораблем Сіндбада під час першої подорожі, коли моряки висадились на «острові»?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Корабель затонув у бурю</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>«Острів» виявився китом, що раптово занурився, і корабель відплив без Сіндбада</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Корабель захопили пірати</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Корабель розбився про скелі</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як Сіндбад урятувався, опинившись сам у морі після зникнення «острова»-кита?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Поплив до берега самостійно</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Учепився за дерев'яне корито, яке прибило хвилями до найближчого острова</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його врятував дельфін</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Корабель повернувся за ним</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чим закінчилась перша подорож для Сіндбада?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він загинув</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він дістався додому з певним прибутком і поклявся більше не плавати — але обіцянку не дотримав</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він залишився жити на острові</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він став рибалкою</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Як Сіндбад опинився сам у долині, повній діамантів, але й оточеній зміями?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його привели туди</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Заснувши, він прокинувся залишеним товаришами в долині під час другої подорожі</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він туди приплив сам</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його викрали</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Яким хитрим способом купці здобували діаманти з тієї небезпечної долини?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спускались на канатах</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кидали в долину великі куски м'яса, до яких прилипали діаманти, а орли приносили м'ясо нагору</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ловили зміїв і обмінювали</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Будували мости</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Як Сіндбад скористався цим способом, щоб вирватись із долини діамантів?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Збудував пліт</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Прив'язав себе до великого куска м'яса, і орел заніс його разом із м'ясом нагору</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підкупив купців</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Знайшов інший вихід пішки</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>З якою небезпекою зіткнувся Сіндбад на острові під час однієї з подорожей?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>З драконом</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З велетнем-людожером, що ловив і смажив моряків по одному щодня</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зі зграєю вовків</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зі зачарованим лісом</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Сіндбад і моряки, що залишились, врятувались від велетня-людожера?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Втекли непомітно вночі</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Засліпили йому очі розпеченим залізом, поки той спав, і втекли до кораблів</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вбили його мечами в бою</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Підкупили його золотом</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що сталося, коли осліплений велетень кинувся в погоню за кораблями біля берега?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не зміг знайти кораблі</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він кидав величезні каменюки в кораблі, потопивши частину з них</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заплив за ними і вибачився</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він покликав на допомогу інших велетнів, які допомогли морякам</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Який страшний звичай Сіндбад виявив на одному з островів, одруживши там?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Звичай прощатися назавжди</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Якщо один з подружжя помирає, другого живцем хоронять разом із покійним</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Звичай дарувати золото</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Звичай вигнання чужинців</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як Сіндбад уник смерті, коли його дружина померла і за звичаєм мали поховати й його?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Втік перед похованням</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У підземній печері для похованих він убивав тих, кого ще приносили живими, забираючи їхні припаси, доки не знайшов вихід</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Місцеві пожаліли і відпустили його</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його врятували моряки з корабля</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що допомогло Сіндбаду зрештою вийти з підземної гробниці на волю?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Магічне заклинання</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він пішов за диким звіром, який знав вузький прохід назовні з печери</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Землетрус відкрив прохід</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його почули зверху і витягли</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Хто такий Старий Моря, якого Сіндбад зустрів і необачно посадив собі на плечі?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Звичайний старий, що просив допомоги</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Хитра істота, яка міцно обхопила Сіндбада ногами за шию і не злазила, змушуючи носити її повсюди</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дух острова</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Морський бог</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Як довго Старий Моря тримав Сіндбада у своїй владі, не злазячи з його плечей?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Один день</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Довгий час, виснажуючи Сіндбада постійним тягарем</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кілька годин</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Цілий рік без перерви</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як Сіндбад зрештою позбувся Старого Моря?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Попросив його злізти</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Напоїв його виноградним вином, доки той не сп'янів і послабив хватку, після чого скинув і вбив його</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підкупив його золотом</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Втік, коли той заснув</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що, попри всі небезпеки, знову й знову штовхало Сіндбада в нові подорожі?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Наказ халіфа</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Невгамовна цікавість і потяг до пригод, навіть після кожної клятви більше не плавати</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бідність</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Втеча від ворогів</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Яку рису характеру Сіндбада підкреслює те, що він кожного разу знаходив вихід зі смертельної небезпеки?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Силу</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кмітливість і вміння спостерігати та вчитися навіть у тварин чи купців</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Багатство</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Магічні здібності</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що, окрім скарбів, Сіндбад привозив додому з кожної подорожі?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого, крім золота</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дивовижні історії та досвід, якими він і ділиться з носильником</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нових друзів-моряків</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Карти островів</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Кому Сіндбад розповідає свої пригоди і чому?</t>
+          <t>Сіндбад розповідає свої пригоди бідному носильнику, щоб показати, якою ціною дістається багатство.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку моральну ідею несе обрамлення казки де Сіндбад говорить з бідняком?</t>
+          <t>Обрамлена розповідь — коли один герой розповідає історію іншому — типова для збірки «Тисяча і одна ніч».</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яка риса Сіндбада є найважливішою для його виживання?</t>
+          <t>Найважливіша риса Сіндбада, що допомагає йому виживати, — фізична сила, а не кмітливість.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Де Сіндбад опинився в полоні у Старого Моря?</t>
+          <t>Старий Моря міцно обхопив Сіндбада ногами за шию і не злазив із нього довгий час.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Як Сіндбад позбувся Старого Моря що сидів у нього на плечах?</t>
+          <t>Сіндбад позбувся Старого Моря, напоївши його вином.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея казок про Сіндбада?</t>
+          <t>Головна ідея казок про Сіндбада — краще ніколи нікуди не подорожувати, бо весь світ небезпечний.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які фантастичні істоти і явища трапляються Сіндбаду?</t>
+          <t>Які небезпеки траплялись Сіндбаду в його подорожах?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Птах Рух</t>
+          <t>Острів-кит</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Острів-кит</t>
+          <t>Велетень-людожер</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Добра фея</t>
+          <t>Мирний відпочинок без пригод</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Старий Моря</t>
+          <t>Старий Моря на плечах</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Казковий велетенський птах такий великий що міг підняти слона — Сіндбад прив'язав себе до його лапи щоб врятуватись</t>
+          <t>Казковий велетенський птах такий великий що міг підняти слона</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Прив'язавшись до орла що підхопив шматок м'яса з долини — купці кидали м'ясо щоб птахи приносили прилиплі діаманти</t>
+          <t>Прив'язавшись до орла що підхопив шматок м'яса з долини</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
